--- a/data/availability/projects/hassan-allam-properties/swanlake-residences-new-cairo.xlsx
+++ b/data/availability/projects/hassan-allam-properties/swanlake-residences-new-cairo.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for swanlake-residences-new-cairo</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -604,7 +614,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Twin Villa</t>
+          <t>Twin House</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1059,7 +1069,6 @@
       <c r="G2" t="n">
         <v>281</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1116,7 +1125,6 @@
       <c r="G3" t="n">
         <v>291</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1149,7 +1157,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Twin Villa</t>
+          <t>Twin House</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1234,7 +1242,6 @@
       <c r="G5" t="n">
         <v>93</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1291,7 +1298,6 @@
       <c r="G6" t="n">
         <v>127</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1409,7 +1415,6 @@
       <c r="G8" t="n">
         <v>155</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1649,7 +1654,6 @@
       <c r="G12" t="n">
         <v>155</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1706,7 +1710,6 @@
       <c r="G13" t="n">
         <v>221</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1763,7 +1766,6 @@
       <c r="G14" t="n">
         <v>497</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
